--- a/code/SFNCovariatesSubListR.xlsx
+++ b/code/SFNCovariatesSubListR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameswyngaarden/Documents/GitHub/rf1-sra-socdoors/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089048D3-45E6-3F41-ABA1-2FFA8982F6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34572BAF-E027-6F40-B343-F0056D2A598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" xr2:uid="{E21B9450-44FE-AB4C-A453-866E41E6C653}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" xr2:uid="{E21B9450-44FE-AB4C-A453-866E41E6C653}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
